--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487142_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487142_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.828</v>
+        <v>6.9029</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5783</v>
+        <v>6.9745</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2497</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>6.6132</v>
@@ -610,13 +610,13 @@
         <v>2.3161</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4198</v>
+        <v>0.4947</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.2687</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5473</v>
+        <v>0.226</v>
       </c>
       <c r="V2" t="n">
         <v>-1.5561</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0704</v>
+        <v>6.2245</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8683999999999999</v>
+        <v>1.6477</v>
       </c>
       <c r="F3" t="n">
-        <v>4.202</v>
+        <v>4.5767</v>
       </c>
       <c r="G3" t="n">
         <v>3.8248</v>
@@ -688,13 +688,13 @@
         <v>2.8951</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.9777</v>
+        <v>-0.8236</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3537</v>
+        <v>-0.5744</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.624</v>
+        <v>-0.2492</v>
       </c>
       <c r="V3" t="n">
         <v>0.3281</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.589</v>
+        <v>3.0946</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.3158</v>
+        <v>-1.8369</v>
       </c>
       <c r="F4" t="n">
-        <v>4.9048</v>
+        <v>4.9316</v>
       </c>
       <c r="G4" t="n">
         <v>0.2591</v>
@@ -766,13 +766,13 @@
         <v>3.0881</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0212</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2942</v>
+        <v>-0.8153</v>
       </c>
       <c r="U4" t="n">
-        <v>0.273</v>
+        <v>0.2997</v>
       </c>
       <c r="V4" t="n">
         <v>1.228</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GOMEZ MERODIO</t>
+          <t>D. TRUEBA TAMAYO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4844</v>
+        <v>2.243</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5062</v>
+        <v>1.7255</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0218</v>
+        <v>0.5174</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1655</v>
+        <v>1.9782</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2165</v>
+        <v>1.8754</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.051</v>
+        <v>0.1028</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7195</v>
+        <v>2.5177</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9897</v>
+        <v>1.1746</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2702</v>
+        <v>1.3431</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.554</v>
+        <v>-0.5395</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2268</v>
+        <v>0.7008</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7808</v>
+        <v>-1.2403</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9301</v>
+        <v>0.193</v>
       </c>
       <c r="Q5" t="n">
+        <v>-0.965</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0717</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.1729</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.1012</v>
+      </c>
+      <c r="V5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.9301</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.4429</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.2161</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-1.2702</v>
-      </c>
       <c r="W5" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. TRUEBA TAMAYO</t>
+          <t>J. GOMEZ MERODIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1845</v>
+        <v>2.2226</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5064</v>
+        <v>2.3247</v>
       </c>
       <c r="F6" t="n">
-        <v>0.678</v>
+        <v>-0.1021</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9782</v>
+        <v>1.1655</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8754</v>
+        <v>4.2165</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1028</v>
+        <v>-3.051</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5177</v>
+        <v>2.7195</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1746</v>
+        <v>3.9897</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3431</v>
+        <v>-1.2702</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5395</v>
+        <v>-1.554</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7008</v>
+        <v>0.2268</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2403</v>
+        <v>-1.7808</v>
       </c>
       <c r="P6" t="n">
-        <v>0.193</v>
+        <v>1.9301</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.158</v>
+        <v>1.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0132</v>
+        <v>0.3973</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0462</v>
+        <v>0.2614</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0595</v>
+        <v>0.1358</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.2702</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1938</v>
+        <v>1.1452</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.4713</v>
+        <v>-3.4931</v>
       </c>
       <c r="F7" t="n">
-        <v>4.6651</v>
+        <v>4.6383</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3163</v>
@@ -1000,13 +1000,13 @@
         <v>3.4741</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6709000000000001</v>
+        <v>-0.7195</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.805</v>
+        <v>-0.8269</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1341</v>
+        <v>0.1074</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3281</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1385</v>
+        <v>1.0388</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2335</v>
+        <v>-0.4136</v>
       </c>
       <c r="F8" t="n">
-        <v>1.372</v>
+        <v>1.4523</v>
       </c>
       <c r="G8" t="n">
         <v>0.162</v>
@@ -1078,13 +1078,13 @@
         <v>2.8951</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6677</v>
+        <v>-0.7674</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1898</v>
+        <v>-0.3698</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4779</v>
+        <v>-0.3976</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2859</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.111</v>
+        <v>-0.4114</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2937</v>
+        <v>-2.5941</v>
       </c>
       <c r="F9" t="n">
         <v>2.1827</v>
@@ -1156,10 +1156,10 @@
         <v>1.7371</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1335</v>
+        <v>-0.4339</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0912</v>
+        <v>-0.3916</v>
       </c>
       <c r="U9" t="n">
         <v>-0.0423</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3527</v>
+        <v>-1.0661</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6913</v>
+        <v>-1.6724</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3386</v>
+        <v>0.6063</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7955</v>
@@ -1234,13 +1234,13 @@
         <v>1.9301</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0145</v>
+        <v>0.3011</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0278</v>
+        <v>0.0466</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0132</v>
+        <v>0.2545</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5717</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7116</v>
+        <v>-1.5936</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.6604</v>
+        <v>-6.3818</v>
       </c>
       <c r="F11" t="n">
-        <v>4.9488</v>
+        <v>4.7882</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5686</v>
@@ -1312,13 +1312,13 @@
         <v>2.7021</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6412</v>
+        <v>-0.5232</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1898</v>
+        <v>-0.9111</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5486</v>
+        <v>0.388</v>
       </c>
       <c r="V11" t="n">
         <v>0.6562</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>18.3133</v>
+        <v>19.8005</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.2067</v>
+        <v>-3.7195</v>
       </c>
       <c r="F12" t="n">
         <v>23.5199</v>
@@ -1390,13 +1390,13 @@
         <v>24.1259</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.0057</v>
+        <v>-2.5184</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.6267</v>
+        <v>-3.1395</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6212</v>
+        <v>0.6211</v>
       </c>
       <c r="V12" t="n">
         <v>-3.6839</v>
@@ -1405,7 +1405,7 @@
         <v>1.9589</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.6429</v>
+        <v>-5.642899999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.3192</v>
+        <v>7.2945</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4559</v>
+        <v>5.0567</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8634</v>
+        <v>2.2378</v>
       </c>
       <c r="G13" t="n">
         <v>5.4095</v>
@@ -1468,13 +1468,13 @@
         <v>1.9301</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9974</v>
+        <v>-0.0221</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.31</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3126</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0.9421</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4906</v>
+        <v>1.6043</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9589</v>
+        <v>0.8587</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5317</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>1.0219</v>
@@ -1546,13 +1546,13 @@
         <v>0.386</v>
       </c>
       <c r="S14" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.1963</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4442</v>
+        <v>0.3441</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3616</v>
+        <v>-0.1477</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1627</v>
+        <v>-0.5142</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.986</v>
+        <v>-5.2879</v>
       </c>
       <c r="F15" t="n">
-        <v>5.1488</v>
+        <v>4.7737</v>
       </c>
       <c r="G15" t="n">
         <v>-2.9046</v>
@@ -1624,13 +1624,13 @@
         <v>1.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>3.106</v>
+        <v>1.4291</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3749</v>
+        <v>0.0731</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7311</v>
+        <v>1.356</v>
       </c>
       <c r="V15" t="n">
         <v>1.9264</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.1084</v>
+        <v>-2.162</v>
       </c>
       <c r="E16" t="n">
         <v>-1.8499</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2585</v>
+        <v>-0.3121</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9408</v>
@@ -1702,13 +1702,13 @@
         <v>0.193</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1097</v>
+        <v>-0.1633</v>
       </c>
       <c r="T16" t="n">
         <v>-0.238</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1282</v>
+        <v>0.0747</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2859</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.4828</v>
+        <v>-2.7018</v>
       </c>
       <c r="E17" t="n">
-        <v>-5.5041</v>
+        <v>-4.8031</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0213</v>
+        <v>2.1012</v>
       </c>
       <c r="G17" t="n">
         <v>-2.5719</v>
@@ -1780,13 +1780,13 @@
         <v>2.1231</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3173</v>
+        <v>0.4637</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1765</v>
+        <v>-0.4755</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8592</v>
+        <v>0.9392</v>
       </c>
       <c r="V17" t="n">
         <v>1.1435</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. NDOYE</t>
+          <t>J. OTERO GONZALEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.6233</v>
+        <v>-3.8536</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7721</v>
+        <v>-4.3309</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.3953</v>
+        <v>0.4773</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.0633</v>
+        <v>-0.0391</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1911</v>
+        <v>-2.7302</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.8722</v>
+        <v>2.6911</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5607</v>
+        <v>1.649</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0559</v>
+        <v>-1.6148</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5048</v>
+        <v>3.2638</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5026</v>
+        <v>-1.6882</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1353</v>
+        <v>-1.1155</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3674</v>
+        <v>-0.5727</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.193</v>
+        <v>-4.8252</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.158</v>
+        <v>-6.9483</v>
       </c>
       <c r="R18" t="n">
-        <v>0.965</v>
+        <v>2.1231</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5752</v>
+        <v>1.053</v>
       </c>
       <c r="T18" t="n">
-        <v>1.363</v>
+        <v>0.3966</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2122</v>
+        <v>0.6563</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9421</v>
+        <v>-0.0422</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1278</v>
+        <v>0.5717</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.0699</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. OTERO GONZALEZ</t>
+          <t>A. REY GUTIERREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.2548</v>
+        <v>-3.9752</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.3309</v>
+        <v>-3.8066</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0761</v>
+        <v>-0.1687</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0391</v>
+        <v>-1.0507</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.7302</v>
+        <v>-0.0382</v>
       </c>
       <c r="I19" t="n">
-        <v>2.6911</v>
+        <v>-1.0125</v>
       </c>
       <c r="J19" t="n">
-        <v>1.649</v>
+        <v>-0.5241</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6148</v>
+        <v>0.0621</v>
       </c>
       <c r="L19" t="n">
-        <v>3.2638</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6882</v>
+        <v>-0.5266</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1155</v>
+        <v>-0.1003</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5727</v>
+        <v>-0.4263</v>
       </c>
       <c r="P19" t="n">
-        <v>-4.8252</v>
+        <v>-2.8951</v>
       </c>
       <c r="Q19" t="n">
-        <v>-6.9483</v>
+        <v>-3.0881</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1231</v>
+        <v>0.193</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6518</v>
+        <v>-0.0294</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3966</v>
+        <v>-0.1943</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2551</v>
+        <v>0.1649</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0422</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. CARPINTERO REVILLA</t>
+          <t>A. GARCIA NAVALON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.3447</v>
+        <v>-4.3614</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.2239</v>
+        <v>-3.0041</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8792</v>
+        <v>-1.3573</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.8871</v>
+        <v>-4.4311</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.9218</v>
+        <v>-2.0606</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9654</v>
+        <v>-2.3705</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.1331</v>
+        <v>-1.855</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.92</v>
+        <v>-0.5848</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2131</v>
+        <v>-1.2702</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.754</v>
+        <v>-2.5761</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0018</v>
+        <v>-1.4758</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2478</v>
+        <v>-1.1003</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.1231</v>
+        <v>-0.386</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.0881</v>
+        <v>-1.158</v>
       </c>
       <c r="R20" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0093</v>
+        <v>0.1699</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0026</v>
+        <v>-0.2769</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0119</v>
+        <v>0.4468</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6562</v>
+        <v>0.2859</v>
       </c>
       <c r="W20" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="X20" t="n">
         <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0.6562</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. REY GUTIERREZ</t>
+          <t>N. NDOYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5097</v>
+        <v>-4.3976</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.2071</v>
+        <v>-0.029</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3025</v>
+        <v>-4.3686</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0507</v>
+        <v>-4.0633</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0382</v>
+        <v>-2.1911</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0125</v>
+        <v>-1.8722</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5241</v>
+        <v>-1.5607</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0621</v>
+        <v>-1.0559</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-0.5048</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5266</v>
+        <v>-2.5026</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1003</v>
+        <v>-1.1353</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4263</v>
+        <v>-1.3674</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.8951</v>
+        <v>-0.193</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.0881</v>
+        <v>-1.158</v>
       </c>
       <c r="R21" t="n">
-        <v>0.193</v>
+        <v>0.965</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5638</v>
+        <v>0.8008</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5949</v>
+        <v>0.5619</v>
       </c>
       <c r="U21" t="n">
-        <v>0.031</v>
+        <v>0.2389</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.9421</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.1278</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-3.0699</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. GARCIA NAVALON</t>
+          <t>E. CARPINTERO REVILLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9622</v>
+        <v>-4.5786</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.605</v>
+        <v>-6.324</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3573</v>
+        <v>1.7454</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.4311</v>
+        <v>-3.8871</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0606</v>
+        <v>-2.9218</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3705</v>
+        <v>-0.9654</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.855</v>
+        <v>-3.1331</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5848</v>
+        <v>-1.92</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2702</v>
+        <v>-1.2131</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5761</v>
+        <v>-0.754</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4758</v>
+        <v>-1.0018</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1003</v>
+        <v>0.2478</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.386</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.158</v>
+        <v>-3.0881</v>
       </c>
       <c r="R22" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.431</v>
+        <v>0.7753</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8778</v>
+        <v>-0.1028</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4468</v>
+        <v>0.8781</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2859</v>
+        <v>0.6562</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-18.3134</v>
+        <v>-17.6456</v>
       </c>
       <c r="E23" t="n">
-        <v>-23.52</v>
+        <v>-23.5201</v>
       </c>
       <c r="F23" t="n">
-        <v>5.206899999999999</v>
+        <v>5.874199999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-13.4572</v>
@@ -2218,25 +2218,25 @@
         <v>-18.1947</v>
       </c>
       <c r="I23" t="n">
-        <v>4.7375</v>
+        <v>4.737500000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.415699999999999</v>
+        <v>-4.4157</v>
       </c>
       <c r="K23" t="n">
-        <v>-8.043100000000001</v>
+        <v>-8.043099999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>3.627400000000001</v>
+        <v>3.6274</v>
       </c>
       <c r="M23" t="n">
-        <v>-9.041700000000001</v>
+        <v>-9.041699999999999</v>
       </c>
       <c r="N23" t="n">
         <v>-10.1518</v>
       </c>
       <c r="O23" t="n">
-        <v>1.1101</v>
+        <v>1.110099999999999</v>
       </c>
       <c r="P23" t="n">
         <v>-12.5455</v>
@@ -2248,13 +2248,13 @@
         <v>11.5804</v>
       </c>
       <c r="S23" t="n">
-        <v>4.0057</v>
+        <v>4.673299999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6211000000000002</v>
+        <v>-0.6209999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>4.626499999999999</v>
+        <v>5.2942</v>
       </c>
       <c r="V23" t="n">
         <v>3.6839</v>
